--- a/data/trans_orig/P1401-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2012</t>
+          <t>Población con diagnóstico de cáncer en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>679055</t>
+          <t>678137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686189</t>
+          <t>686190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1289212</t>
+          <t>1289178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296454</t>
+          <t>1296449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670218</t>
+          <t>669756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679936</t>
+          <t>679943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>689641</t>
+          <t>689424</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704874</t>
+          <t>704996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1365942</t>
+          <t>1365910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1383077</t>
+          <t>1383364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>603089</t>
+          <t>602561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612594</t>
+          <t>612539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582928</t>
+          <t>582554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>602753</t>
+          <t>602917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1190176</t>
+          <t>1190327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1212990</t>
+          <t>1213227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>39036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>413821</t>
+          <t>415129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426135</t>
+          <t>426306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417834</t>
+          <t>417176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>435460</t>
+          <t>435269</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>838692</t>
+          <t>838193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859362</t>
+          <t>860095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14951</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34828</t>
+          <t>35950</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287333</t>
+          <t>287749</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304392</t>
+          <t>304697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334480</t>
+          <t>334509</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348009</t>
+          <t>348024</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628954</t>
+          <t>627832</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>648831</t>
+          <t>648729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26736</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234947</t>
+          <t>235433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246717</t>
+          <t>246710</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371304</t>
+          <t>370691</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384574</t>
+          <t>383651</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>612094</t>
+          <t>611800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>629197</t>
+          <t>628342</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27811</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>53228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,74 +3148,74 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>71617</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>56327</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>93964</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>110782</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>89974</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>135408</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>71617</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>55781</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>90732</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>110782</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>90381</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>136569</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3372390</t>
+          <t>3373551</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3398968</t>
+          <t>3399440</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,77 +3261,77 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3483481</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3461134</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3498771</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6871095</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6846469</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6891903</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>98,41%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3483481</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3464366</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3499317</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6405</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6871095</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6845308</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6891496</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2016</t>
+          <t>Población con diagnóstico de cáncer en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,97 +3711,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4054,82 +4054,82 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4924</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>976</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5544</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558000</t>
+          <t>558620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149136</t>
+          <t>1149148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663312</t>
+          <t>664456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643684</t>
+          <t>643893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656501</t>
+          <t>657030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1311188</t>
+          <t>1311513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325254</t>
+          <t>1325137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22455</t>
+          <t>23703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632100</t>
+          <t>632845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643724</t>
+          <t>643474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626622</t>
+          <t>625374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641801</t>
+          <t>641370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1263685</t>
+          <t>1264033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1282583</t>
+          <t>1282737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467246</t>
+          <t>466740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475974</t>
+          <t>475934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>473673</t>
+          <t>474666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489146</t>
+          <t>490010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>946567</t>
+          <t>945741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963255</t>
+          <t>963337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28100</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322747</t>
+          <t>321876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332324</t>
+          <t>332275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>349662</t>
+          <t>349178</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>366398</t>
+          <t>366459</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>676855</t>
+          <t>677431</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>696037</t>
+          <t>695843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26433</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42294</t>
+          <t>38540</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237166</t>
+          <t>237884</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>250313</t>
+          <t>250446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>373736</t>
+          <t>374388</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>392957</t>
+          <t>393148</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614873</t>
+          <t>618627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640183</t>
+          <t>640884</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>41430</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>94528</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81462</t>
+          <t>82250</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123133</t>
+          <t>122264</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3353773</t>
+          <t>3352920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3373822</t>
+          <t>3374310</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3453633</t>
+          <t>3450014</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3488944</t>
+          <t>3489436</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6815759</t>
+          <t>6816628</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6857430</t>
+          <t>6856642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2023</t>
+          <t>Población con diagnóstico de cáncer en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,97 +6690,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3603</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310311</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709584</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415043</t>
+          <t>415028</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506829</t>
+          <t>506844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>925520</t>
+          <t>926001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527022</t>
+          <t>528137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532165</t>
+          <t>532453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539824</t>
+          <t>539822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1064110</t>
+          <t>1063783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074569</t>
+          <t>1074548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>25573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38735</t>
+          <t>37864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>866498</t>
+          <t>867082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882673</t>
+          <t>882890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>686449</t>
+          <t>686263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>699823</t>
+          <t>699798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1558751</t>
+          <t>1559622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1581584</t>
+          <t>1582233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30171</t>
+          <t>29663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>51223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529207</t>
+          <t>529715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546065</t>
+          <t>546715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>517866</t>
+          <t>517620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>530004</t>
+          <t>529749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1052829</t>
+          <t>1051396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1073514</t>
+          <t>1072283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>22482</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>30852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>17813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46296</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>343957</t>
+          <t>344344</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>355972</t>
+          <t>356320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>577716</t>
+          <t>577357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>602927</t>
+          <t>601676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>928739</t>
+          <t>928455</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958627</t>
+          <t>957222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24267</t>
+          <t>24415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>28219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45588</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255075</t>
+          <t>255649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>268506</t>
+          <t>268637</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>400967</t>
+          <t>400819</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>413051</t>
+          <t>412828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>661541</t>
+          <t>661438</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>678671</t>
+          <t>678910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51219</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86048</t>
+          <t>85695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62072</t>
+          <t>60692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92266</t>
+          <t>93196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124444</t>
+          <t>123640</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170844</t>
+          <t>170753</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3367410</t>
+          <t>3367763</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3402239</t>
+          <t>3400496</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3562756</t>
+          <t>3561826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3592950</t>
+          <t>3594330</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6937636</t>
+          <t>6937727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6984036</t>
+          <t>6984840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1401-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Edad-trans_orig.xlsx
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>678137</t>
+          <t>678855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686190</t>
+          <t>686196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1289178</t>
+          <t>1289079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296449</t>
+          <t>1296446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>669756</t>
+          <t>670272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679943</t>
+          <t>679942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>689424</t>
+          <t>689279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704996</t>
+          <t>705009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1365910</t>
+          <t>1365766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1383364</t>
+          <t>1382778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31710</t>
+          <t>32247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>37693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>602561</t>
+          <t>601859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612539</t>
+          <t>612554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582554</t>
+          <t>582017</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>602917</t>
+          <t>602459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1190327</t>
+          <t>1191187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1213227</t>
+          <t>1213285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>29849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17134</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39036</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415129</t>
+          <t>415041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426306</t>
+          <t>426362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>417176</t>
+          <t>417951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>435269</t>
+          <t>435555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>838193</t>
+          <t>838499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>860095</t>
+          <t>858626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>21130</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287749</t>
+          <t>288656</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304697</t>
+          <t>303913</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334509</t>
+          <t>334396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348024</t>
+          <t>347774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>627832</t>
+          <t>628939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>648729</t>
+          <t>649623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27030</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235433</t>
+          <t>236304</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246710</t>
+          <t>246746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>370691</t>
+          <t>370811</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383651</t>
+          <t>384546</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>611800</t>
+          <t>612909</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628342</t>
+          <t>628960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53228</t>
+          <t>54935</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93964</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>89974</t>
+          <t>91287</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135408</t>
+          <t>134369</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3373551</t>
+          <t>3371844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3399440</t>
+          <t>3398134</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3461134</t>
+          <t>3466282</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3498771</t>
+          <t>3500248</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6846469</t>
+          <t>6847508</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6891903</t>
+          <t>6890590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558620</t>
+          <t>558022</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149148</t>
+          <t>1148616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664456</t>
+          <t>664420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643893</t>
+          <t>642747</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657030</t>
+          <t>656991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1311513</t>
+          <t>1311064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325137</t>
+          <t>1325099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>31477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632845</t>
+          <t>633069</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643474</t>
+          <t>643927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625374</t>
+          <t>625675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641370</t>
+          <t>641111</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1264033</t>
+          <t>1263648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1282737</t>
+          <t>1282540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>10878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>28229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>466740</t>
+          <t>466941</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475934</t>
+          <t>475981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474666</t>
+          <t>474394</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490010</t>
+          <t>489207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>945741</t>
+          <t>946538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963337</t>
+          <t>963889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>15600</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34661</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>321876</t>
+          <t>321456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332275</t>
+          <t>331503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>349178</t>
+          <t>349464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>366459</t>
+          <t>366379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>677431</t>
+          <t>676095</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>695843</t>
+          <t>696492</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25781</t>
+          <t>26790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38540</t>
+          <t>40838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237884</t>
+          <t>237617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>250446</t>
+          <t>250860</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>374388</t>
+          <t>373379</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>393148</t>
+          <t>392775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>618627</t>
+          <t>616329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640884</t>
+          <t>640083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41430</t>
+          <t>42386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>53433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94528</t>
+          <t>90386</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82250</t>
+          <t>82952</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122264</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3352920</t>
+          <t>3351964</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3374310</t>
+          <t>3373149</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3450014</t>
+          <t>3454156</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3489436</t>
+          <t>3491109</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6816628</t>
+          <t>6815540</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6856642</t>
+          <t>6855940</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>975</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -7141,17 +7141,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421926</t>
+          <t>475070</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415028</t>
+          <t>466516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7176,27 +7176,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>510564</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506844</t>
+          <t>496568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7211,27 +7211,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>932490</t>
+          <t>975178</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926001</t>
+          <t>964508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,32 +7441,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7484,27 +7484,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>533559</t>
+          <t>617178</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528137</t>
+          <t>609691</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>536932</t>
+          <t>616314</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532453</t>
+          <t>610888</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539822</t>
+          <t>619122</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,32 +7554,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1070491</t>
+          <t>1233492</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1063783</t>
+          <t>1226631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074548</t>
+          <t>1237698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077973</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077973</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077973</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18569</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>28728</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37864</t>
+          <t>39377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>876358</t>
+          <t>688742</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>867082</t>
+          <t>680654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882890</t>
+          <t>693717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>694075</t>
+          <t>716704</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>686263</t>
+          <t>708341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>699798</t>
+          <t>722290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1570432</t>
+          <t>1405446</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1559622</t>
+          <t>1394797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1582233</t>
+          <t>1413563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>885651</t>
+          <t>698387</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885651</t>
+          <t>698387</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>885651</t>
+          <t>698387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711836</t>
+          <t>735787</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711836</t>
+          <t>735787</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711836</t>
+          <t>735787</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1597486</t>
+          <t>1434174</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1597486</t>
+          <t>1434174</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1597486</t>
+          <t>1434174</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29663</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>27721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39104</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30336</t>
+          <t>31576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>54257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>538792</t>
+          <t>586424</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529715</t>
+          <t>575614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546715</t>
+          <t>594101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>524723</t>
+          <t>585181</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>517620</t>
+          <t>577922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>529749</t>
+          <t>590937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1063515</t>
+          <t>1171605</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1051396</t>
+          <t>1158800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1072283</t>
+          <t>1181481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559378</t>
+          <t>607414</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559378</t>
+          <t>607414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559378</t>
+          <t>607414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543241</t>
+          <t>605643</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>543241</t>
+          <t>605643</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>543241</t>
+          <t>605643</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1102619</t>
+          <t>1213057</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1102619</t>
+          <t>1213057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1102619</t>
+          <t>1213057</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>17677</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>12159</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>26394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30852</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>29362</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46580</t>
+          <t>48283</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -8513,32 +8513,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>351165</t>
+          <t>387867</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>344344</t>
+          <t>379150</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>356320</t>
+          <t>393385</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8548,32 +8548,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>589782</t>
+          <t>418333</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>577357</t>
+          <t>410677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601676</t>
+          <t>423764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>940947</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>928455</t>
+          <t>795761</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>957222</t>
+          <t>814682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366826</t>
+          <t>405544</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366826</t>
+          <t>405544</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366826</t>
+          <t>405544</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608209</t>
+          <t>438501</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608209</t>
+          <t>438501</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608209</t>
+          <t>438501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975035</t>
+          <t>844044</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975035</t>
+          <t>844044</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975035</t>
+          <t>844044</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>21834</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26246</t>
+          <t>30714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,22 +8778,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>25946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>36528</t>
+          <t>40789</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28219</t>
+          <t>31329</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45691</t>
+          <t>52282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>262794</t>
+          <t>287423</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255649</t>
+          <t>278543</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>268637</t>
+          <t>294029</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,27 +8891,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>407807</t>
+          <t>444928</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>400819</t>
+          <t>437937</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>412828</t>
+          <t>450320</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>670601</t>
+          <t>732351</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>661438</t>
+          <t>720858</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>678910</t>
+          <t>741811</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>309257</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425234</t>
+          <t>463883</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425234</t>
+          <t>463883</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425234</t>
+          <t>463883</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707129</t>
+          <t>773140</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707129</t>
+          <t>773140</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707129</t>
+          <t>773140</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>58261</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85695</t>
+          <t>90426</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60692</t>
+          <t>71138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93196</t>
+          <t>98188</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>159325</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>123640</t>
+          <t>140385</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170753</t>
+          <t>181701</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3384581</t>
+          <t>3450497</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3367763</t>
+          <t>3434578</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3400496</t>
+          <t>3466743</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3577082</t>
+          <t>3644079</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3561826</t>
+          <t>3630709</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3594330</t>
+          <t>3657759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6961663</t>
+          <t>7094576</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6937727</t>
+          <t>7072200</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6984840</t>
+          <t>7113516</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
